--- a/training/hydraulic-series/am/AM_Standard_Hydraulic_Unit.xlsx
+++ b/training/hydraulic-series/am/AM_Standard_Hydraulic_Unit.xlsx
@@ -1872,7 +1872,7 @@
     <t xml:space="preserve">AM Calendar — ระบบไฮดรอลิก · ปี ……</t>
   </si>
   <si>
-    <t xml:space="preserve">D = ทุกวัน · W = รายสัปดาห์ · Q = ทุก 3 เดือน (มี.ค. มิ.ย. ก.ย. ธ.ค. *) · S = ทุก 6 เดือน (มิ.ย. ธ.ค. *) · A = ทุก 1 ปี (ธ.ค. *) · เดือนที่ตรวจตามรอบเป็นข้อเสนอ ให้วางตามแผนหยุดเครื่อง</t>
+    <t xml:space="preserve">D = ทุกวัน · W = รายสัปดาห์ · Q = ทุก 3 เดือน (มี.ค. มิ.ย. ก.ย. ธ.ค. *) · S = ทุก 6 เดือน (มิ.ย. ธ.ค. *) · A = ทุก 1 ปี (ธ.ค. *) · เดือนตามรอบเป็นข้อเสนอ เกลี่ยกับอีกระบบแล้ว (AM_Calendar_Combined.xlsx) ให้วางตามแผนหยุดเครื่อง</t>
   </si>
   <si>
     <t xml:space="preserve">กิจกรรม (CILT)</t>
